--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_15/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_15/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99998499509518</v>
+        <v>41.78910698341235</v>
       </c>
       <c r="B2" t="n">
-        <v>155.745383754573</v>
+        <v>78.07177320186793</v>
       </c>
       <c r="C2" t="n">
-        <v>47.76936880730202</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="D2" t="n">
-        <v>5.030929603332775</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E2" t="n">
-        <v>4.894186216035965</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F2" t="n">
-        <v>12.74889891749177</v>
+        <v>4.08401858099314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01778702218547362</v>
+        <v>0.3580501558917902</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9279212586430705</v>
+        <v>-0.003242188247305976</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9464990227396252</v>
+        <v>-0.5393256727140772</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9692438421362853</v>
+        <v>-0.007913572433008303</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.663297540761317e-05</v>
+        <v>-0.001135419239060512</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220068609063508</v>
+        <v>-0.5285940465560823</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02332788554733272</v>
+        <v>-3.279031728975479e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40.26963656156759</v>
+        <v>41.78910698341235</v>
       </c>
       <c r="B3" t="n">
-        <v>153.6114416604304</v>
+        <v>77.58240821188002</v>
       </c>
       <c r="C3" t="n">
-        <v>47.49361926720055</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="D3" t="n">
-        <v>10.01074886377354</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E3" t="n">
-        <v>2.910196358277848</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F3" t="n">
-        <v>3.989492743182196</v>
+        <v>4.08401858099314</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4626662549072069</v>
+        <v>0.3580501558917902</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.003441854160723875</v>
+        <v>-0.003242188247305976</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5354162799447583</v>
+        <v>-0.5393256727140772</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.990956752765508e-05</v>
+        <v>-0.007913572433008303</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0002125267763614829</v>
+        <v>-0.001135419239060512</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1758169931142657</v>
+        <v>-0.5285940465560823</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03138634873962451</v>
+        <v>-3.279031728975479e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>40.26963656156759</v>
+        <v>99.99999999957858</v>
       </c>
       <c r="B4" t="n">
-        <v>154.8943391531379</v>
+        <v>105.9798471914669</v>
       </c>
       <c r="C4" t="n">
-        <v>47.49361926720055</v>
+        <v>45.50014553215833</v>
       </c>
       <c r="D4" t="n">
-        <v>10.01074886377354</v>
+        <v>5.709251360203378</v>
       </c>
       <c r="E4" t="n">
-        <v>2.752827221616104</v>
+        <v>3.213919991917548</v>
       </c>
       <c r="F4" t="n">
-        <v>3.989492743182196</v>
+        <v>12.9499454058226</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4626662549072069</v>
+        <v>0.01752996067092474</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.003441854160723875</v>
+        <v>-0.918168862763705</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5354162799447583</v>
+        <v>-0.9400450567573126</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.990956752765508e-05</v>
+        <v>-0.9636783402199217</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002125267763614829</v>
+        <v>-0.0003870640554394715</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1758169931142657</v>
+        <v>-0.5874999999969973</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03138634873962451</v>
+        <v>-3.234047962735742e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89.11153082934493</v>
+        <v>45.63324888440405</v>
       </c>
       <c r="B5" t="n">
-        <v>198.034519003509</v>
+        <v>77.88824874223724</v>
       </c>
       <c r="C5" t="n">
-        <v>47.70369266212663</v>
+        <v>45.50016915445911</v>
       </c>
       <c r="D5" t="n">
-        <v>6.493200516777332</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E5" t="n">
-        <v>4.954491418742349</v>
+        <v>2.929881155895793</v>
       </c>
       <c r="F5" t="n">
-        <v>10.64543627336101</v>
+        <v>4.611907222010551</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0258561922207462</v>
+        <v>0.2573382701770977</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9007496649993662</v>
+        <v>-0.2273677497055343</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9286813333329031</v>
+        <v>-0.6197055329783576</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9530913808848031</v>
+        <v>-0.291830554936685</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.07848278747019836</v>
+        <v>-0.04336814409015451</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5406693490369369</v>
+        <v>-0.5390105762678923</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02448173388096726</v>
+        <v>-3.758987980106987e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52.06108345297626</v>
+        <v>88.02017257112816</v>
       </c>
       <c r="B6" t="n">
-        <v>193.2675443815903</v>
+        <v>120.7710543915862</v>
       </c>
       <c r="C6" t="n">
-        <v>47.49527924390517</v>
+        <v>45.50914213044069</v>
       </c>
       <c r="D6" t="n">
-        <v>9.421650844876726</v>
+        <v>6.97896206979506</v>
       </c>
       <c r="E6" t="n">
-        <v>4.868462569787527</v>
+        <v>3.042627756970275</v>
       </c>
       <c r="F6" t="n">
-        <v>5.139589278545056</v>
+        <v>10.5565978249218</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1741463755425758</v>
+        <v>0.02649124393851867</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5332660465418747</v>
+        <v>-0.8830970831559271</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7408876203043993</v>
+        <v>-0.9175480455059853</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6352790426213879</v>
+        <v>-0.9418348407354553</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0382053924668301</v>
+        <v>-0.02594626220691152</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2638999236099769</v>
+        <v>-0.5021437295692881</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03136375634235482</v>
+        <v>-0.002031584542376008</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96.18012143686954</v>
+        <v>53.14248821867324</v>
       </c>
       <c r="B7" t="n">
-        <v>160.7522923448442</v>
+        <v>115.074959157151</v>
       </c>
       <c r="C7" t="n">
-        <v>47.49336152215126</v>
+        <v>45.5092290721396</v>
       </c>
       <c r="D7" t="n">
-        <v>5.536436972822822</v>
+        <v>9.641366001870519</v>
       </c>
       <c r="E7" t="n">
-        <v>2.658555850358198</v>
+        <v>4.859854967202339</v>
       </c>
       <c r="F7" t="n">
-        <v>11.9757063515933</v>
+        <v>5.301562870675438</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02014317886705675</v>
+        <v>0.158142124846488</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9197571869135356</v>
+        <v>-0.5037174963940806</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9411280507043723</v>
+        <v>-0.7294256858073178</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9645687937964293</v>
+        <v>-0.6060823514417114</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01437428991680928</v>
+        <v>-0.04092862576755707</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5934722137675472</v>
+        <v>-0.263604445099048</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03138985666749591</v>
+        <v>-0.002050904919910918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41.77766910859151</v>
+        <v>75.20265613380052</v>
       </c>
       <c r="B8" t="n">
-        <v>142.4549720368008</v>
+        <v>109.9063593403868</v>
       </c>
       <c r="C8" t="n">
-        <v>47.49912986835302</v>
+        <v>45.50964900805797</v>
       </c>
       <c r="D8" t="n">
-        <v>9.930891736754031</v>
+        <v>9.353011987115485</v>
       </c>
       <c r="E8" t="n">
-        <v>2.439528633036677</v>
+        <v>3.386322255936121</v>
       </c>
       <c r="F8" t="n">
-        <v>4.117733303073932</v>
+        <v>8.578092999638734</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4015419787183549</v>
+        <v>0.04557973881617471</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1063925092889223</v>
+        <v>-0.8165012587390829</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5722288409260753</v>
+        <v>-0.8783688444713</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1351023031978267</v>
+        <v>-0.8943424957145766</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.00341900527757384</v>
+        <v>-0.2749302691442957</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1870821013955539</v>
+        <v>-0.4108189249533287</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03131134907843301</v>
+        <v>-0.002144224012881474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80.70929534798846</v>
+        <v>43.57740853246673</v>
       </c>
       <c r="B9" t="n">
-        <v>169.5456817213586</v>
+        <v>77.04524657979483</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59371189742997</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="D9" t="n">
-        <v>7.16696402414089</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E9" t="n">
-        <v>4.973470807149357</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F9" t="n">
-        <v>9.118958736005569</v>
+        <v>4.323818032032301</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03601343120785922</v>
+        <v>0.3058054500275895</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8688370334556255</v>
+        <v>-0.1192565693548418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9088809026679691</v>
+        <v>-0.5805495353634726</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9322035546170464</v>
+        <v>-0.1583592012295638</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01770677145976803</v>
+        <v>-0.02002562636342832</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.477904064103825</v>
+        <v>-0.5332531554610338</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04816577146425926</v>
+        <v>-3.279031728975479e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76.53731568098233</v>
+        <v>97.83844959720122</v>
       </c>
       <c r="B10" t="n">
-        <v>183.4840950248734</v>
+        <v>137.6911913022417</v>
       </c>
       <c r="C10" t="n">
-        <v>47.49922698216834</v>
+        <v>46.03879242755316</v>
       </c>
       <c r="D10" t="n">
-        <v>8.425149596633728</v>
+        <v>6.264846243609412</v>
       </c>
       <c r="E10" t="n">
-        <v>3.518321294495837</v>
+        <v>4.862126428979479</v>
       </c>
       <c r="F10" t="n">
-        <v>8.612349862224756</v>
+        <v>12.575090361055</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04348802647757997</v>
+        <v>0.01882056054418931</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8471927912287053</v>
+        <v>-0.9130093548857214</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8959619349312702</v>
+        <v>-0.936600872923705</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9169963373138033</v>
+        <v>-0.9606231043977738</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2288239581486121</v>
+        <v>-0.1117931557285897</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4467390850793958</v>
+        <v>-0.5720989533800587</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0313100273527186</v>
+        <v>-0.1197316505673697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93.56101235748216</v>
+        <v>72.7870759219233</v>
       </c>
       <c r="B11" t="n">
-        <v>193.3491029567616</v>
+        <v>121.7773065244597</v>
       </c>
       <c r="C11" t="n">
-        <v>47.49525223912211</v>
+        <v>45.50125408897029</v>
       </c>
       <c r="D11" t="n">
-        <v>5.821762220036264</v>
+        <v>8.687747058867336</v>
       </c>
       <c r="E11" t="n">
-        <v>4.582329987556745</v>
+        <v>2.780830413657337</v>
       </c>
       <c r="F11" t="n">
-        <v>11.45424842260188</v>
+        <v>8.020375459463002</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02202015707125523</v>
+        <v>0.05075319440345296</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9133814894978253</v>
+        <v>-0.7987895505136895</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9368999206827733</v>
+        <v>-0.8687275693280436</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9608086929170692</v>
+        <v>-0.880676165219579</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01241102750553631</v>
+        <v>-0.1200588396013438</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5739072863142034</v>
+        <v>-0.3936079159437035</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03136412387931196</v>
+        <v>-0.0002786864378434561</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>46.42217221208863</v>
+        <v>49.46625716459985</v>
       </c>
       <c r="B12" t="n">
-        <v>182.8122503528604</v>
+        <v>118.6329217416153</v>
       </c>
       <c r="C12" t="n">
-        <v>47.49719970130564</v>
+        <v>45.54328854061877</v>
       </c>
       <c r="D12" t="n">
-        <v>9.689857307601061</v>
+        <v>9.714155411180334</v>
       </c>
       <c r="E12" t="n">
-        <v>4.67516298214468</v>
+        <v>4.9174521919714</v>
       </c>
       <c r="F12" t="n">
-        <v>4.546308732599358</v>
+        <v>4.873564257041467</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2682967550885728</v>
+        <v>0.2065994300942386</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3458316114473585</v>
+        <v>-0.38737315473782</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.663023174305525</v>
+        <v>-0.6812089799177987</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4287737560295238</v>
+        <v>-0.4789527996927513</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01535862892625036</v>
+        <v>-0.02329311968877579</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2217768634396018</v>
+        <v>-0.245996928734499</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03133761878487541</v>
+        <v>-0.009619675693060409</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.12000225362699</v>
+        <v>44.64790224613458</v>
       </c>
       <c r="B13" t="n">
-        <v>149.9778790609668</v>
+        <v>106.4648273973924</v>
       </c>
       <c r="C13" t="n">
-        <v>47.49337637264615</v>
+        <v>45.50014765408605</v>
       </c>
       <c r="D13" t="n">
-        <v>9.815135327208228</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E13" t="n">
-        <v>2.581134977471074</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F13" t="n">
-        <v>4.432936080894041</v>
+        <v>4.472171329410786</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2992158359559818</v>
+        <v>0.2792132823137439</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2883415525254192</v>
+        <v>-0.176013121409054</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6404398224499469</v>
+        <v>-0.6005625523991107</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3610480795136543</v>
+        <v>-0.2286156963855124</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.02322955089507225</v>
+        <v>-0.01806692371409651</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2120495630496598</v>
+        <v>-0.5327700475588524</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03138965455123784</v>
+        <v>-3.281201912216924e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97.63747420183346</v>
+        <v>54.52030379778572</v>
       </c>
       <c r="B14" t="n">
-        <v>168.8420277107223</v>
+        <v>115.6945826445437</v>
       </c>
       <c r="C14" t="n">
-        <v>47.60467862700175</v>
+        <v>45.5092290721396</v>
       </c>
       <c r="D14" t="n">
-        <v>6.344882145596025</v>
+        <v>9.466602252257188</v>
       </c>
       <c r="E14" t="n">
-        <v>4.82275363778871</v>
+        <v>4.868161442506672</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4781694292211</v>
+        <v>5.440531058316052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01928235427520603</v>
+        <v>0.1436259144365053</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9229139892705074</v>
+        <v>-0.5336336065752837</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.943173188237542</v>
+        <v>-0.7409385447581409</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9663871836390984</v>
+        <v>-0.6361353043099163</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2958184781270262</v>
+        <v>-0.005022830412920618</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.604358740542949</v>
+        <v>-0.2634571645592232</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02750441983871408</v>
+        <v>-0.002050904919910918</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.30693348888382</v>
+        <v>90.30279523298395</v>
       </c>
       <c r="B15" t="n">
-        <v>191.5223638193921</v>
+        <v>103.9032054173474</v>
       </c>
       <c r="C15" t="n">
-        <v>47.50158928208348</v>
+        <v>45.50944849759539</v>
       </c>
       <c r="D15" t="n">
-        <v>9.70729434570022</v>
+        <v>7.775370018760391</v>
       </c>
       <c r="E15" t="n">
-        <v>4.98918421445927</v>
+        <v>2.881357518378041</v>
       </c>
       <c r="F15" t="n">
-        <v>4.647122500886143</v>
+        <v>11.19924330681823</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2499346237948545</v>
+        <v>0.02448049886727963</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3811739669489155</v>
+        <v>-0.89104318490985</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6771467574581922</v>
+        <v>-0.9224146455658384</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4694082031709049</v>
+        <v>-0.9469817675875595</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.03073019125275239</v>
+        <v>-0.2617179358099821</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.228386091871613</v>
+        <v>-0.5184074160350107</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.03127787628818583</v>
+        <v>-0.002099666132308053</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45.69135870488176</v>
+        <v>44.31489178086954</v>
       </c>
       <c r="B16" t="n">
-        <v>154.622638220483</v>
+        <v>117.1463062051102</v>
       </c>
       <c r="C16" t="n">
-        <v>47.49413155673637</v>
+        <v>45.50101135588779</v>
       </c>
       <c r="D16" t="n">
-        <v>9.70729434570022</v>
+        <v>6.554936365016936</v>
       </c>
       <c r="E16" t="n">
-        <v>4.984846172142297</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F16" t="n">
-        <v>4.471098719946303</v>
+        <v>4.42689801182296</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2849202404710274</v>
+        <v>0.2871654142477272</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3144826294376049</v>
+        <v>-0.157606343197255</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6506627481947231</v>
+        <v>-0.5937835741277759</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3921017408066608</v>
+        <v>-0.2056317400768741</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.009100747068511845</v>
+        <v>-0.01135577406999095</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2163176355811843</v>
+        <v>-0.5306609812788403</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.03137937644376186</v>
+        <v>-0.0002247457528423147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62.1355759913172</v>
+        <v>60.99513150754389</v>
       </c>
       <c r="B17" t="n">
-        <v>175.1348178513397</v>
+        <v>104.8735116940913</v>
       </c>
       <c r="C17" t="n">
-        <v>47.49429974962997</v>
+        <v>45.51024489869965</v>
       </c>
       <c r="D17" t="n">
-        <v>8.961221117456954</v>
+        <v>9.007052632032346</v>
       </c>
       <c r="E17" t="n">
-        <v>2.915028504660706</v>
+        <v>4.368762729674557</v>
       </c>
       <c r="F17" t="n">
-        <v>6.388703122583165</v>
+        <v>6.227609408851949</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09079079378892313</v>
+        <v>0.09500788679991708</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7216265952090484</v>
+        <v>-0.6684238699270308</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8285597745379385</v>
+        <v>-0.8035684987535434</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8163145642106996</v>
+        <v>-0.7693489550099785</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09404493238832513</v>
+        <v>-0.02521415326547346</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3391570853651477</v>
+        <v>-0.3210268991489147</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.03137708732689629</v>
+        <v>-0.002276644155477792</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53.83545060201074</v>
+        <v>48.47904637463917</v>
       </c>
       <c r="B18" t="n">
-        <v>154.3859228001401</v>
+        <v>120.5318039980818</v>
       </c>
       <c r="C18" t="n">
-        <v>47.50221437089035</v>
+        <v>45.57058610345538</v>
       </c>
       <c r="D18" t="n">
-        <v>9.70729434570022</v>
+        <v>9.725624790146103</v>
       </c>
       <c r="E18" t="n">
-        <v>4.98918421445927</v>
+        <v>2.944321160293089</v>
       </c>
       <c r="F18" t="n">
-        <v>5.419349592664301</v>
+        <v>4.763196176011609</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1543258871102622</v>
+        <v>0.2228277723328214</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5765519097127242</v>
+        <v>-0.3499179118672987</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7599218413864134</v>
+        <v>-0.6662502530901365</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.679427604512219</v>
+        <v>-0.4362129526590727</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1174880433360876</v>
+        <v>-0.01249056914454382</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.27715456993978</v>
+        <v>-0.2385928478097937</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0312693687864747</v>
+        <v>-0.01568580076786064</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>70.17736498324754</v>
+        <v>51.90048059202411</v>
       </c>
       <c r="B19" t="n">
-        <v>152.7231015453239</v>
+        <v>115.074959157151</v>
       </c>
       <c r="C19" t="n">
-        <v>47.49415568579053</v>
+        <v>45.5092290721396</v>
       </c>
       <c r="D19" t="n">
-        <v>7.962036020788594</v>
+        <v>9.440874180540204</v>
       </c>
       <c r="E19" t="n">
-        <v>4.720374071699918</v>
+        <v>4.859854967202339</v>
       </c>
       <c r="F19" t="n">
-        <v>7.424119184569219</v>
+        <v>5.106804366304832</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05846287971187803</v>
+        <v>0.1722232686892891</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8044472736981321</v>
+        <v>-0.4682437160538502</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8719655527202057</v>
+        <v>-0.7144611446172064</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.88499662775459</v>
+        <v>-0.5683050288892707</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01152288757824426</v>
+        <v>-0.00117206057481213</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3992298098883341</v>
+        <v>-0.2642536044401809</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.03137904804567294</v>
+        <v>-0.002050904919910918</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40.55026196240472</v>
+        <v>47.60792042391878</v>
       </c>
       <c r="B20" t="n">
-        <v>155.398020683714</v>
+        <v>121.5791981625091</v>
       </c>
       <c r="C20" t="n">
-        <v>47.49361926720055</v>
+        <v>45.50095739268324</v>
       </c>
       <c r="D20" t="n">
-        <v>10.00007827248659</v>
+        <v>9.732534670547121</v>
       </c>
       <c r="E20" t="n">
-        <v>2.686499779687197</v>
+        <v>4.483047321729396</v>
       </c>
       <c r="F20" t="n">
-        <v>4.013785023613139</v>
+        <v>4.662952406125807</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4504540264245365</v>
+        <v>0.2384865808877427</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.02375503013260338</v>
+        <v>-0.3142733710836989</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5425870137560127</v>
+        <v>-0.652244222204472</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.02708663951688962</v>
+        <v>-0.3947802047521444</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001605306648108182</v>
+        <v>-0.0003334021507292298</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1779132844265115</v>
+        <v>-0.2320594031793908</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.03138634873962451</v>
+        <v>-0.0002127539296081782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>72.62940564699635</v>
+        <v>62.34688045029194</v>
       </c>
       <c r="B21" t="n">
-        <v>182.7324518135251</v>
+        <v>121.6302743658774</v>
       </c>
       <c r="C21" t="n">
-        <v>47.26372523941448</v>
+        <v>45.50927213046388</v>
       </c>
       <c r="D21" t="n">
-        <v>7.870557040859806</v>
+        <v>9.196163861231829</v>
       </c>
       <c r="E21" t="n">
-        <v>3.050227786923387</v>
+        <v>3.14386907179531</v>
       </c>
       <c r="F21" t="n">
-        <v>7.835508779282518</v>
+        <v>6.46271952661651</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05189564770819356</v>
+        <v>0.08797048042317948</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8227453880227628</v>
+        <v>-0.6849290689839421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.882086163462286</v>
+        <v>-0.8103804368293284</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8990146059043703</v>
+        <v>-0.7837898867213685</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03312688131174038</v>
+        <v>-0.06102926778486936</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4175467246271869</v>
+        <v>-0.3192215232083301</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.04771079249070127</v>
+        <v>-0.002060473436418381</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>44.27660035138833</v>
+        <v>93.79645745392773</v>
       </c>
       <c r="B22" t="n">
-        <v>185.9277806850699</v>
+        <v>121.7847308547038</v>
       </c>
       <c r="C22" t="n">
-        <v>47.49420569072085</v>
+        <v>46.03879242755316</v>
       </c>
       <c r="D22" t="n">
-        <v>9.815135327208228</v>
+        <v>6.655138423087956</v>
       </c>
       <c r="E22" t="n">
-        <v>2.294218163696558</v>
+        <v>4.862126428979479</v>
       </c>
       <c r="F22" t="n">
-        <v>4.344798458193067</v>
+        <v>11.74341041209302</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3213956821980862</v>
+        <v>0.0215515403063679</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.247598864385718</v>
+        <v>-0.9021588067632164</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6247819532212332</v>
+        <v>-0.9295415688311415</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3119695674431662</v>
+        <v>-0.9540153181947272</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01227466458161775</v>
+        <v>-0.1010001266723143</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2057492920295727</v>
+        <v>-0.543299759359235</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.03137836747512802</v>
+        <v>-0.1197316505673697</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>60.20831841909985</v>
+        <v>63.68293134145918</v>
       </c>
       <c r="B23" t="n">
-        <v>198.042266481027</v>
+        <v>119.18331787365</v>
       </c>
       <c r="C23" t="n">
-        <v>47.49437923541439</v>
+        <v>45.52703195834866</v>
       </c>
       <c r="D23" t="n">
-        <v>8.710118674226877</v>
+        <v>8.973356965795647</v>
       </c>
       <c r="E23" t="n">
-        <v>4.105884498974085</v>
+        <v>2.952131981366195</v>
       </c>
       <c r="F23" t="n">
-        <v>6.060461730416717</v>
+        <v>6.616178317834001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1014514874161496</v>
+        <v>0.08137679949050956</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6951798258104321</v>
+        <v>-0.7039025823325022</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8155403253419137</v>
+        <v>-0.8196964136326724</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.79285973304947</v>
+        <v>-0.8009060283626743</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.009477842679918202</v>
+        <v>-0.03497741458238202</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3247603369131285</v>
+        <v>-0.3287408858078966</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0313760055198964</v>
+        <v>-0.00600710185525738</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>84.0549259283742</v>
+        <v>65.34340569580436</v>
       </c>
       <c r="B24" t="n">
-        <v>198.2374906602404</v>
+        <v>106.932115485759</v>
       </c>
       <c r="C24" t="n">
-        <v>47.48613604880808</v>
+        <v>46.24715722360464</v>
       </c>
       <c r="D24" t="n">
-        <v>6.825609739886902</v>
+        <v>8.629075567393059</v>
       </c>
       <c r="E24" t="n">
-        <v>4.98736958857109</v>
+        <v>3.03495206976782</v>
       </c>
       <c r="F24" t="n">
-        <v>9.694178807030312</v>
+        <v>6.826009245172344</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03138458324673362</v>
+        <v>0.07411466658223027</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.88307608203679</v>
+        <v>-0.725328319277701</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9175741020422798</v>
+        <v>-0.8303928680200688</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9417576610903876</v>
+        <v>-0.8197940689809564</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0269201398287915</v>
+        <v>-1.215357140607146e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5028961578299272</v>
+        <v>-0.3405717655826062</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.03168057677702865</v>
+        <v>-0.166034938578809</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81.96033311820806</v>
+        <v>43.03024232375059</v>
       </c>
       <c r="B25" t="n">
-        <v>169.5456817213586</v>
+        <v>76.20677950296745</v>
       </c>
       <c r="C25" t="n">
-        <v>46.59371189742997</v>
+        <v>45.50093644390703</v>
       </c>
       <c r="D25" t="n">
-        <v>7.590536943580486</v>
+        <v>6.435132534645304</v>
       </c>
       <c r="E25" t="n">
-        <v>4.836666210346177</v>
+        <v>2.877911383430426</v>
       </c>
       <c r="F25" t="n">
-        <v>9.445668776122776</v>
+        <v>4.226109738663997</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03430285845980556</v>
+        <v>0.3203805492954015</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.87430473629489</v>
+        <v>-0.08591117123551667</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9121371979003767</v>
+        <v>-0.5685687108910576</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9359011516007778</v>
+        <v>-0.1157844870710543</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1516256595204761</v>
+        <v>-0.0003338882007302951</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4872494034821545</v>
+        <v>-0.5368682821583373</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.04816577146425926</v>
+        <v>-0.0002080986460066547</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>74.01496486840499</v>
+        <v>42.24239306767059</v>
       </c>
       <c r="B26" t="n">
-        <v>156.0352245258335</v>
+        <v>77.04524657979483</v>
       </c>
       <c r="C26" t="n">
-        <v>47.49922698216834</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="D26" t="n">
-        <v>8.09960611904085</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E26" t="n">
-        <v>3.848835944949533</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F26" t="n">
-        <v>8.10018261710904</v>
+        <v>4.143850699418937</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04866618786306282</v>
+        <v>0.343775519915355</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8320085911257776</v>
+        <v>-0.03451339538715955</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8872898649710403</v>
+        <v>-0.5502939842945475</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9059311965046605</v>
+        <v>-0.04906832523485539</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1178085794541366</v>
+        <v>-0.01338774466965946</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4278969486260714</v>
+        <v>-0.5316159537844707</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0313100273527186</v>
+        <v>-3.279031728975479e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>65.12619537121914</v>
+        <v>78.16511956802022</v>
       </c>
       <c r="B27" t="n">
-        <v>197.9670231954791</v>
+        <v>133.5241692723979</v>
       </c>
       <c r="C27" t="n">
-        <v>46.06857334213476</v>
+        <v>45.50624742347005</v>
       </c>
       <c r="D27" t="n">
-        <v>8.721856518786582</v>
+        <v>7.804530844305093</v>
       </c>
       <c r="E27" t="n">
-        <v>4.995315336701861</v>
+        <v>4.665542448670228</v>
       </c>
       <c r="F27" t="n">
-        <v>6.783600219367711</v>
+        <v>8.796119059355481</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0765765108153332</v>
+        <v>0.03951046207313617</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7571484135166454</v>
+        <v>-0.8361936036959251</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8466854475056775</v>
+        <v>-0.8896726251565248</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8467303674385935</v>
+        <v>-0.9091387757368627</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.06502194988017719</v>
+        <v>-0.01995954858403692</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.3614972206687262</v>
+        <v>-0.431926476922144</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.04696025131346837</v>
+        <v>-0.001388316326676325</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>85.71760331529656</v>
+        <v>57.28267922246634</v>
       </c>
       <c r="B28" t="n">
-        <v>152.4144766314272</v>
+        <v>115.3496473486049</v>
       </c>
       <c r="C28" t="n">
-        <v>47.49363296608764</v>
+        <v>45.58838826536718</v>
       </c>
       <c r="D28" t="n">
-        <v>6.873604365606898</v>
+        <v>9.376541137906312</v>
       </c>
       <c r="E28" t="n">
-        <v>4.880828455195406</v>
+        <v>4.862093723785296</v>
       </c>
       <c r="F28" t="n">
-        <v>10.02969644164153</v>
+        <v>5.789273070996911</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02942257308256627</v>
+        <v>0.1197483402351013</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8893183959516817</v>
+        <v>-0.5965029829320451</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9214405355645636</v>
+        <v>-0.7689126882534784</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9458268631075898</v>
+        <v>-0.6997772605881289</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08441935260565168</v>
+        <v>-0.02667361583057403</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5153164738486323</v>
+        <v>-0.2831390894600727</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.03138616229682804</v>
+        <v>-0.01964183674826203</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>48.99003582746145</v>
+        <v>95.35913727668949</v>
       </c>
       <c r="B29" t="n">
-        <v>160.7359893482935</v>
+        <v>120.8035849538579</v>
       </c>
       <c r="C29" t="n">
-        <v>47.49363858889367</v>
+        <v>45.51251746583851</v>
       </c>
       <c r="D29" t="n">
-        <v>9.446875299457444</v>
+        <v>6.4308560347373</v>
       </c>
       <c r="E29" t="n">
-        <v>4.152599620645283</v>
+        <v>2.848799946861995</v>
       </c>
       <c r="F29" t="n">
-        <v>4.781875979310655</v>
+        <v>12.02994834258375</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2185027735956751</v>
+        <v>0.02041838929640601</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4420650362854148</v>
+        <v>-0.9065911307131004</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7021282466005175</v>
+        <v>-0.9324160326298693</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5377112075994612</v>
+        <v>-0.9567468024763204</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0002021303179285417</v>
+        <v>-0.07308066680415121</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.2409589837034135</v>
+        <v>-0.5544338530964126</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.03138608577005071</v>
+        <v>-0.002781659075225262</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>42.6354861081749</v>
+        <v>92.00477434006748</v>
       </c>
       <c r="B30" t="n">
-        <v>159.4997958849951</v>
+        <v>110.266682224365</v>
       </c>
       <c r="C30" t="n">
-        <v>47.52169173611865</v>
+        <v>45.50634987786188</v>
       </c>
       <c r="D30" t="n">
-        <v>10.11933082340814</v>
+        <v>6.551490186367268</v>
       </c>
       <c r="E30" t="n">
-        <v>4.840056447035701</v>
+        <v>4.64965826704264</v>
       </c>
       <c r="F30" t="n">
-        <v>4.242823240035793</v>
+        <v>11.31405486342391</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3725320414292259</v>
+        <v>0.02290362093327143</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1580085115544912</v>
+        <v>-0.8967902503614009</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.591035484377206</v>
+        <v>-0.92613813547794</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2007759144891546</v>
+        <v>-0.9506606282176672</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.05099754625152809</v>
+        <v>-0.009918253692704366</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.1934900541979701</v>
+        <v>-0.5305340171729808</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.03078156209866956</v>
+        <v>-0.001411083969305726</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>49.77253110500776</v>
+        <v>57.80229582014454</v>
       </c>
       <c r="B31" t="n">
-        <v>153.5779933035091</v>
+        <v>111.5901817393698</v>
       </c>
       <c r="C31" t="n">
-        <v>46.37083891876537</v>
+        <v>45.50072769069672</v>
       </c>
       <c r="D31" t="n">
-        <v>9.508664959644765</v>
+        <v>9.531644237126411</v>
       </c>
       <c r="E31" t="n">
-        <v>3.528658771627469</v>
+        <v>4.649908498841937</v>
       </c>
       <c r="F31" t="n">
-        <v>4.885585691714691</v>
+        <v>5.88778243971719</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2061111159880856</v>
+        <v>0.1160344156996861</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.467333823575211</v>
+        <v>-0.6068654190418612</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7126549022734069</v>
+        <v>-0.7735951345112194</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5652879753994848</v>
+        <v>-0.7099410418111806</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0004924418832200766</v>
+        <v>-0.06332637265017023</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.2468042779900335</v>
+        <v>-0.2868413577185298</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.04299445864876354</v>
+        <v>-0.0001617090437157354</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>41.07530458426316</v>
+        <v>85.45734153545918</v>
       </c>
       <c r="B32" t="n">
-        <v>145.1107219933533</v>
+        <v>76.56395156032981</v>
       </c>
       <c r="C32" t="n">
-        <v>47.49379845971684</v>
+        <v>45.50015820810212</v>
       </c>
       <c r="D32" t="n">
-        <v>10.01074886377354</v>
+        <v>7.305984207254145</v>
       </c>
       <c r="E32" t="n">
-        <v>2.726575653986523</v>
+        <v>3.015502313686032</v>
       </c>
       <c r="F32" t="n">
-        <v>4.066143015044188</v>
+        <v>10.0994992524882</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4288722296929779</v>
+        <v>0.02923925783884899</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0601972566829487</v>
+        <v>-0.8728943013399174</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5555460100941593</v>
+        <v>-0.9112847770104419</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.07508263470822947</v>
+        <v>-0.9350318802113176</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.01029824500807385</v>
+        <v>-0.05130999501243368</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.1818353894229848</v>
+        <v>-0.4838835584401465</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.03138390991713736</v>
+        <v>-3.515735602657721e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>44.03364285698805</v>
+        <v>71.49302678366303</v>
       </c>
       <c r="B33" t="n">
-        <v>153.6114416604304</v>
+        <v>127.0630748805916</v>
       </c>
       <c r="C33" t="n">
-        <v>47.49422748102288</v>
+        <v>46.24715722360464</v>
       </c>
       <c r="D33" t="n">
-        <v>9.823699951416126</v>
+        <v>8.569512747087215</v>
       </c>
       <c r="E33" t="n">
-        <v>2.638082171031991</v>
+        <v>4.654019769203032</v>
       </c>
       <c r="F33" t="n">
-        <v>4.321498795558415</v>
+        <v>7.80497315042307</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3282133430620167</v>
+        <v>0.05401819782645709</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2352592991871307</v>
+        <v>-0.7881407749395716</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6200842668724174</v>
+        <v>-0.8629739263838253</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2969239716404806</v>
+        <v>-0.8722439825096773</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.01083491586047537</v>
+        <v>-0.0885454664205171</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.203934382604991</v>
+        <v>-0.384387815833599</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0313780709076164</v>
+        <v>-0.166034938578809</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>43.33686797605971</v>
+        <v>55.89547028441679</v>
       </c>
       <c r="B34" t="n">
-        <v>188.0179959003717</v>
+        <v>121.7847308547038</v>
       </c>
       <c r="C34" t="n">
-        <v>47.49490338043677</v>
+        <v>46.58055785460358</v>
       </c>
       <c r="D34" t="n">
-        <v>9.815135327208228</v>
+        <v>9.378205926800632</v>
       </c>
       <c r="E34" t="n">
-        <v>4.952425261990584</v>
+        <v>4.87406806128447</v>
       </c>
       <c r="F34" t="n">
-        <v>4.24854389197919</v>
+        <v>5.646522748876034</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3486801241873819</v>
+        <v>0.1312578028681143</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1984002014318395</v>
+        <v>-0.5662813818566997</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6061934602961428</v>
+        <v>-0.755280593437206</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.251522643679629</v>
+        <v>-0.6695286171113545</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.308682716058625e-05</v>
+        <v>-0.0282648042681911</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.1987294256583854</v>
+        <v>-0.2732552257764695</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.03136887187004523</v>
+        <v>-0.2401239676896848</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91.11481600645379</v>
+        <v>50.33804230509696</v>
       </c>
       <c r="B35" t="n">
-        <v>198.7625760215631</v>
+        <v>127.0629217317971</v>
       </c>
       <c r="C35" t="n">
-        <v>47.48613604880808</v>
+        <v>46.13043291183384</v>
       </c>
       <c r="D35" t="n">
-        <v>6.825609739886902</v>
+        <v>9.666172827498702</v>
       </c>
       <c r="E35" t="n">
-        <v>4.98736958857109</v>
+        <v>4.685999773435457</v>
       </c>
       <c r="F35" t="n">
-        <v>11.14041526847806</v>
+        <v>4.991773724910832</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02410528426721336</v>
+        <v>0.1937329373921581</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9066438308628906</v>
+        <v>-0.4099584926000973</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9324392039468894</v>
+        <v>-0.6886761254125029</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9567262624210255</v>
+        <v>-0.502592380872202</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.2155943333801633</v>
+        <v>-0.003189742679725541</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5556340289988958</v>
+        <v>-0.2336585514238159</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.03168057677702865</v>
+        <v>-0.140096202629743</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>71.08000626257957</v>
+        <v>51.30703525223521</v>
       </c>
       <c r="B36" t="n">
-        <v>154.7247938182347</v>
+        <v>118.6329217416153</v>
       </c>
       <c r="C36" t="n">
-        <v>47.50224516792858</v>
+        <v>45.54328854061877</v>
       </c>
       <c r="D36" t="n">
-        <v>7.883301688935573</v>
+        <v>9.724160214195157</v>
       </c>
       <c r="E36" t="n">
-        <v>2.904378816080933</v>
+        <v>4.9174521919714</v>
       </c>
       <c r="F36" t="n">
-        <v>7.557048500603156</v>
+        <v>5.094153222760138</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05588196522927728</v>
+        <v>0.1803246928922465</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8115084729969114</v>
+        <v>-0.4422294181593429</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8758542534804128</v>
+        <v>-0.7019888423271842</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8904639603812937</v>
+        <v>-0.5384250348421749</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.01001990641031327</v>
+        <v>-0.01525133059506512</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4059726031860669</v>
+        <v>-0.2405626261721758</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.03126894963666395</v>
+        <v>-0.009619675693060409</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>42.33679958436572</v>
+        <v>83.42700256480185</v>
       </c>
       <c r="B37" t="n">
-        <v>138.390043101084</v>
+        <v>124.6488142933629</v>
       </c>
       <c r="C37" t="n">
-        <v>47.4991225868738</v>
+        <v>45.50955565361274</v>
       </c>
       <c r="D37" t="n">
-        <v>9.889188373232033</v>
+        <v>7.304918420924044</v>
       </c>
       <c r="E37" t="n">
-        <v>2.43971133579527</v>
+        <v>4.984331081550684</v>
       </c>
       <c r="F37" t="n">
-        <v>4.164013025057612</v>
+        <v>9.695629277250404</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3814710909922848</v>
+        <v>0.03165773822826033</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1409494948018437</v>
+        <v>-0.8639701436081889</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5848618784858266</v>
+        <v>-0.9059253482924884</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1793197506400577</v>
+        <v>-0.928939567596815</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.002195139430377874</v>
+        <v>-0.004047525506439054</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.191258845037722</v>
+        <v>-0.4694173932742132</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.03131144817986676</v>
+        <v>-0.00212347858060763</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67.51793529099497</v>
+        <v>55.46058873229838</v>
       </c>
       <c r="B38" t="n">
-        <v>183.3642455469178</v>
+        <v>111.6493357181323</v>
       </c>
       <c r="C38" t="n">
-        <v>47.49922698216834</v>
+        <v>46.08161539527334</v>
       </c>
       <c r="D38" t="n">
-        <v>8.320668262003434</v>
+        <v>9.531644237126411</v>
       </c>
       <c r="E38" t="n">
-        <v>4.950508804203058</v>
+        <v>4.649908498841937</v>
       </c>
       <c r="F38" t="n">
-        <v>7.071046395193012</v>
+        <v>5.600233142318491</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0671510776643517</v>
+        <v>0.1351469560863378</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7813272841186401</v>
+        <v>-0.5620294266770492</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8594449221596213</v>
+        <v>-0.7547457357664036</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.866636806339944</v>
+        <v>-0.6662977776935093</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04683215590681474</v>
+        <v>-0.06302802348638525</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.3793636846453335</v>
+        <v>-0.2805555551049319</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0313100273527186</v>
+        <v>-0.1292478656162975</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>57.56296213181849</v>
+        <v>68.18425128770902</v>
       </c>
       <c r="B39" t="n">
-        <v>169.1362449555429</v>
+        <v>108.3753939360795</v>
       </c>
       <c r="C39" t="n">
-        <v>47.49716289147199</v>
+        <v>46.23935951344627</v>
       </c>
       <c r="D39" t="n">
-        <v>9.068139717289981</v>
+        <v>8.629075567393059</v>
       </c>
       <c r="E39" t="n">
-        <v>3.851092511290553</v>
+        <v>2.877847141727917</v>
       </c>
       <c r="F39" t="n">
-        <v>5.771090350149074</v>
+        <v>7.272595796520803</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1198662248892967</v>
+        <v>0.06377490030887716</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6523129089013794</v>
+        <v>-0.7571254536033856</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7948854758033498</v>
+        <v>-0.8466120381988053</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.75331429114716</v>
+        <v>-0.8469009265147932</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.04575173810815545</v>
+        <v>-0.04653540187736425</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.3049993409866005</v>
+        <v>-0.3608127904249268</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.03133811976924652</v>
+        <v>-0.1643021140991721</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56.02171067260868</v>
+        <v>48.00630740222132</v>
       </c>
       <c r="B40" t="n">
-        <v>150.7676669834124</v>
+        <v>120.7715648931987</v>
       </c>
       <c r="C40" t="n">
-        <v>47.46910215144461</v>
+        <v>45.50095739268324</v>
       </c>
       <c r="D40" t="n">
-        <v>9.70729434570022</v>
+        <v>9.748280320653063</v>
       </c>
       <c r="E40" t="n">
-        <v>3.529413604769131</v>
+        <v>4.368762729674557</v>
       </c>
       <c r="F40" t="n">
-        <v>5.712780286740294</v>
+        <v>4.7110518438044</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1333809007351485</v>
+        <v>0.2311866666993005</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6229834322526613</v>
+        <v>-0.3308808159198956</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7810192609251234</v>
+        <v>-0.6587409560697066</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7252093902582512</v>
+        <v>-0.4141724034413943</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1458928379839579</v>
+        <v>-0.009050015487699391</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.293486085114931</v>
+        <v>-0.2350473055166599</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.03237575814481986</v>
+        <v>-0.0002127539296081782</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>58.07332135135611</v>
+        <v>59.3128535991017</v>
       </c>
       <c r="B41" t="n">
-        <v>160.7359893482935</v>
+        <v>126.9732718850459</v>
       </c>
       <c r="C41" t="n">
-        <v>47.49362231187239</v>
+        <v>45.53255581509944</v>
       </c>
       <c r="D41" t="n">
-        <v>9.446875299457444</v>
+        <v>9.21462513059849</v>
       </c>
       <c r="E41" t="n">
-        <v>4.152599620645283</v>
+        <v>4.365000443038493</v>
       </c>
       <c r="F41" t="n">
-        <v>5.919151894810588</v>
+        <v>6.032607759738846</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1165319607618608</v>
+        <v>0.1053247104143101</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.660803726111814</v>
+        <v>-0.6356668560836741</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7988165935783947</v>
+        <v>-0.7869655897276708</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7612182461594034</v>
+        <v>-0.7378433817438863</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1275866122093791</v>
+        <v>-0.02080480706013137</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.3088117599438646</v>
+        <v>-0.2976040818935995</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.03138630730143113</v>
+        <v>-0.007234625577653975</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>43.4446902745144</v>
+        <v>43.04164903782084</v>
       </c>
       <c r="B42" t="n">
-        <v>187.2466734261705</v>
+        <v>76.20677950296745</v>
       </c>
       <c r="C42" t="n">
-        <v>47.49361926720055</v>
+        <v>45.50093644390703</v>
       </c>
       <c r="D42" t="n">
-        <v>9.830057796432822</v>
+        <v>6.435132534645304</v>
       </c>
       <c r="E42" t="n">
-        <v>2.985214581331711</v>
+        <v>2.892982631293523</v>
       </c>
       <c r="F42" t="n">
-        <v>4.262550957689026</v>
+        <v>4.227651942498785</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3454671632617415</v>
+        <v>0.3200614696639893</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.2042262622264368</v>
+        <v>-0.08662612305272602</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6083708667756978</v>
+        <v>-0.568824676070677</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2587383900019403</v>
+        <v>-0.116703454126325</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.004457444544030204</v>
+        <v>-0.0006531605045889186</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.1995348657462844</v>
+        <v>-0.5369443269188057</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.03138634873962451</v>
+        <v>-0.0002080986460066547</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47.95858860077443</v>
+        <v>59.52559851512095</v>
       </c>
       <c r="B43" t="n">
-        <v>155.379516750697</v>
+        <v>119.5652771246155</v>
       </c>
       <c r="C43" t="n">
-        <v>47.54538163717928</v>
+        <v>45.51024489869965</v>
       </c>
       <c r="D43" t="n">
-        <v>9.692118339922041</v>
+        <v>9.19806609947349</v>
       </c>
       <c r="E43" t="n">
-        <v>3.590071010593459</v>
+        <v>4.368762729674557</v>
       </c>
       <c r="F43" t="n">
-        <v>4.718417335544145</v>
+        <v>6.058076374733528</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2373867454175988</v>
+        <v>0.1039463150852159</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.4056031386265657</v>
+        <v>-0.6394692467761155</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6870492720643588</v>
+        <v>-0.7887460745111403</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4970593670152453</v>
+        <v>-0.7414701773845136</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.0372660218855992</v>
+        <v>-0.01994092659679454</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.2332540009973079</v>
+        <v>-0.2991198894202367</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.02984605077785998</v>
+        <v>-0.002276644155477792</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>41.02782747316572</v>
+        <v>42.24239306767059</v>
       </c>
       <c r="B44" t="n">
-        <v>160.0239373608777</v>
+        <v>77.26255125856206</v>
       </c>
       <c r="C44" t="n">
-        <v>47.49922698216834</v>
+        <v>45.50014755642781</v>
       </c>
       <c r="D44" t="n">
-        <v>10.01074886377354</v>
+        <v>6.548895372296088</v>
       </c>
       <c r="E44" t="n">
-        <v>3.848835944949533</v>
+        <v>3.009425543323951</v>
       </c>
       <c r="F44" t="n">
-        <v>4.061823706327927</v>
+        <v>4.143850699418937</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4307804534560333</v>
+        <v>0.343775519915355</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.05697195883480429</v>
+        <v>-0.03451339538715955</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5543922341901613</v>
+        <v>-0.5502939842945475</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.07085775711244877</v>
+        <v>-0.04906832523485539</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.00981548114242722</v>
+        <v>-0.01338774466965946</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.1814807320925108</v>
+        <v>-0.5316159537844707</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0313100273527186</v>
+        <v>-3.279031728975479e-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67.51793529099497</v>
+        <v>50.58512253890981</v>
       </c>
       <c r="B45" t="n">
-        <v>183.6973605463622</v>
+        <v>127.0629217317971</v>
       </c>
       <c r="C45" t="n">
-        <v>47.49922698216834</v>
+        <v>46.13062033105594</v>
       </c>
       <c r="D45" t="n">
-        <v>8.320668262003434</v>
+        <v>9.666172827498702</v>
       </c>
       <c r="E45" t="n">
-        <v>2.869433405470261</v>
+        <v>4.685999773435457</v>
       </c>
       <c r="F45" t="n">
-        <v>7.071046395193012</v>
+        <v>5.021159050524281</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0671510776643517</v>
+        <v>0.1902307707739155</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.7813272841186401</v>
+        <v>-0.418394291793778</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8594449221596213</v>
+        <v>-0.6921302393845472</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.866636806339944</v>
+        <v>-0.5120178647316191</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.04683215590681474</v>
+        <v>-0.006445710028777906</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.3793636846453335</v>
+        <v>-0.2354189980897324</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0313100273527186</v>
+        <v>-0.1401378513457646</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>54.01371297580344</v>
+        <v>66.17045283930996</v>
       </c>
       <c r="B46" t="n">
-        <v>155.398020683714</v>
+        <v>127.0630748805916</v>
       </c>
       <c r="C46" t="n">
-        <v>47.49376184551022</v>
+        <v>46.24355517947267</v>
       </c>
       <c r="D46" t="n">
-        <v>9.858182161520272</v>
+        <v>9.214070024007203</v>
       </c>
       <c r="E46" t="n">
-        <v>2.686499779687197</v>
+        <v>4.654019769203032</v>
       </c>
       <c r="F46" t="n">
-        <v>5.473019503967041</v>
+        <v>7.075743851093332</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1527060948059998</v>
+        <v>0.07125774853751188</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5804568332742991</v>
+        <v>-0.7347730622144927</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7616313517927208</v>
+        <v>-0.8350444600247851</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6833152960242288</v>
+        <v>-0.8279035402299706</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1463501950599431</v>
+        <v>-0.1344748627562651</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.2784862023022361</v>
+        <v>-0.3464644764800834</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.03138440823901027</v>
+        <v>-0.1652344843272598</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50.73209516749897</v>
+        <v>79.88034892311141</v>
       </c>
       <c r="B47" t="n">
-        <v>153.7933064680979</v>
+        <v>121.6919811170567</v>
       </c>
       <c r="C47" t="n">
-        <v>47.49714638246087</v>
+        <v>45.50350195669397</v>
       </c>
       <c r="D47" t="n">
-        <v>9.766568433030031</v>
+        <v>8.569512747087215</v>
       </c>
       <c r="E47" t="n">
-        <v>4.418009725003624</v>
+        <v>4.654019769203032</v>
       </c>
       <c r="F47" t="n">
-        <v>5.052027963870814</v>
+        <v>9.272028318302226</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1924963971260793</v>
+        <v>0.03690912379275292</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4960141294358462</v>
+        <v>-0.8457691195073689</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7247177628631289</v>
+        <v>-0.8950856154813401</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.5960317372403481</v>
+        <v>-0.916067214666287</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.08730412393487505</v>
+        <v>-0.2156992180966918</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2539722884471877</v>
+        <v>-0.4441474860771688</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.03133834445802482</v>
+        <v>-0.000778212598662037</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>59.53903466360668</v>
+        <v>70.32457914281329</v>
       </c>
       <c r="B48" t="n">
-        <v>198.5051713942583</v>
+        <v>108.3753939360795</v>
       </c>
       <c r="C48" t="n">
-        <v>46.37083891876537</v>
+        <v>45.50260582906399</v>
       </c>
       <c r="D48" t="n">
-        <v>8.883422521390553</v>
+        <v>8.629075567393059</v>
       </c>
       <c r="E48" t="n">
-        <v>3.528658771627469</v>
+        <v>2.877847141727917</v>
       </c>
       <c r="F48" t="n">
-        <v>6.003329013715132</v>
+        <v>7.593239035534754</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1058357631951831</v>
+        <v>0.05716922000027173</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6849750760115511</v>
+        <v>-0.7778970698183449</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.810538568798236</v>
+        <v>-0.8575236410563004</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.7835898926683915</v>
+        <v>-0.8640070501516076</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01385843457058886</v>
+        <v>-0.06701229126806366</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.3197607405904782</v>
+        <v>-0.3760626263925447</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.04299445864876354</v>
+        <v>-0.0005790731253299541</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48.26689699393538</v>
+        <v>79.32040056471988</v>
       </c>
       <c r="B49" t="n">
-        <v>155.379516750697</v>
+        <v>133.3068645390884</v>
       </c>
       <c r="C49" t="n">
-        <v>47.54543188481505</v>
+        <v>45.50624742347005</v>
       </c>
       <c r="D49" t="n">
-        <v>9.692118339922041</v>
+        <v>7.804530844305093</v>
       </c>
       <c r="E49" t="n">
-        <v>2.626651994413806</v>
+        <v>4.663508361890151</v>
       </c>
       <c r="F49" t="n">
-        <v>4.753113748082043</v>
+        <v>9.010462105898101</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2317436990974621</v>
+        <v>0.03760040256274946</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.41670175001638</v>
+        <v>-0.8428918660323326</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6915847566016533</v>
+        <v>-0.893515370988424</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5094978525261192</v>
+        <v>-0.9140187255813864</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.04137379036780091</v>
+        <v>-0.04349918719391845</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.235557086192546</v>
+        <v>-0.4401578540236291</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02984406650481479</v>
+        <v>-0.001388316326676325</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>55.61225672908452</v>
+        <v>66.67008413717728</v>
       </c>
       <c r="B50" t="n">
-        <v>153.5544140324145</v>
+        <v>126.7137576921965</v>
       </c>
       <c r="C50" t="n">
-        <v>46.34680344645206</v>
+        <v>46.24355517947267</v>
       </c>
       <c r="D50" t="n">
-        <v>9.215222648974919</v>
+        <v>9.214070024007203</v>
       </c>
       <c r="E50" t="n">
-        <v>4.98918421445927</v>
+        <v>4.691963525971956</v>
       </c>
       <c r="F50" t="n">
-        <v>5.542922635211075</v>
+        <v>7.15393568487677</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1362008780583346</v>
+        <v>0.06938482779437856</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6153916253978352</v>
+        <v>-0.7404829698456634</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7776640348556896</v>
+        <v>-0.8379479971972639</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7179409217640066</v>
+        <v>-0.8327960406537145</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.02366533422970909</v>
+        <v>-0.141680057808454</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.2904274356056065</v>
+        <v>-0.3500243494773881</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.04278211833176836</v>
+        <v>-0.1652344843272598</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>85.71760331529656</v>
+        <v>81.94325057272778</v>
       </c>
       <c r="B51" t="n">
-        <v>176.577338410808</v>
+        <v>71.47058636130687</v>
       </c>
       <c r="C51" t="n">
-        <v>47.49363296608764</v>
+        <v>45.50601255327741</v>
       </c>
       <c r="D51" t="n">
-        <v>6.873604365606898</v>
+        <v>7.708876089404795</v>
       </c>
       <c r="E51" t="n">
-        <v>4.880828455195406</v>
+        <v>2.931169371811664</v>
       </c>
       <c r="F51" t="n">
-        <v>10.02969644164153</v>
+        <v>9.489166184113856</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02942257308256627</v>
+        <v>0.03369164999468165</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8893183959516817</v>
+        <v>-0.8581650908488939</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9214405355645636</v>
+        <v>-0.9030086064819816</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9458268631075898</v>
+        <v>-0.9250511435323573</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.08441935260565168</v>
+        <v>-0.1644569069663765</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5153164738486323</v>
+        <v>-0.4491258085151303</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.03138616229682804</v>
+        <v>-0.001336122950534729</v>
       </c>
     </row>
   </sheetData>
